--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.45517096077328</v>
+        <v>4.298965281125659</v>
       </c>
       <c r="D2" t="n">
-        <v>14.98657964461687</v>
+        <v>2.435319192250242</v>
       </c>
       <c r="E2" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F2" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.53374621976962</v>
+        <v>7.074233760712564</v>
       </c>
       <c r="D3" t="n">
-        <v>24.37261242225447</v>
+        <v>3.960549518616352</v>
       </c>
       <c r="E3" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F3" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.00773713935556</v>
+        <v>2.601257285145278</v>
       </c>
       <c r="D4" t="n">
-        <v>10.24235826251836</v>
+        <v>1.664383217659234</v>
       </c>
       <c r="E4" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F4" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>84.42892693984389</v>
+        <v>13.71970062772463</v>
       </c>
       <c r="D5" t="n">
-        <v>63.26507992345098</v>
+        <v>10.28057548756079</v>
       </c>
       <c r="E5" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F5" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.53598340671501</v>
+        <v>3.987097303591189</v>
       </c>
       <c r="D6" t="n">
-        <v>12.84838128841118</v>
+        <v>2.087861959366817</v>
       </c>
       <c r="E6" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F6" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.43403074324364</v>
+        <v>8.033029995777092</v>
       </c>
       <c r="D7" t="n">
-        <v>48.64094016459703</v>
+        <v>7.904152776747017</v>
       </c>
       <c r="E7" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F7" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.79186985911738</v>
+        <v>5.328678852106574</v>
       </c>
       <c r="D8" t="n">
-        <v>32.52216023720297</v>
+        <v>5.284851038545484</v>
       </c>
       <c r="E8" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F8" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47501435859538</v>
+        <v>7.87718983327175</v>
       </c>
       <c r="D9" t="n">
-        <v>49.04561793356814</v>
+        <v>7.969912914204823</v>
       </c>
       <c r="E9" t="n">
-        <v>19.979426219785</v>
+        <v>3.246656760715063</v>
       </c>
       <c r="F9" t="n">
-        <v>18.48331718669332</v>
+        <v>3.003539042837664</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
